--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.28211629539094</v>
+        <v>7.195843898001028</v>
       </c>
       <c r="D2" t="n">
-        <v>45.11833410041739</v>
+        <v>7.331729291317827</v>
       </c>
       <c r="E2" t="n">
-        <v>13.69346397396203</v>
+        <v>2.22518789576883</v>
       </c>
       <c r="F2" t="n">
-        <v>7.916411587498134</v>
+        <v>1.286416882968447</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.55567808028585</v>
+        <v>4.315297688046452</v>
       </c>
       <c r="D3" t="n">
-        <v>25.5242172703851</v>
+        <v>4.147685306437579</v>
       </c>
       <c r="E3" t="n">
-        <v>13.69346397396203</v>
+        <v>2.22518789576883</v>
       </c>
       <c r="F3" t="n">
-        <v>7.916411587498134</v>
+        <v>1.286416882968447</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.84967031388232</v>
+        <v>4.200571426005877</v>
       </c>
       <c r="D4" t="n">
-        <v>26.2002364859873</v>
+        <v>4.257538428972936</v>
       </c>
       <c r="E4" t="n">
-        <v>13.69346397396203</v>
+        <v>2.22518789576883</v>
       </c>
       <c r="F4" t="n">
-        <v>7.916411587498134</v>
+        <v>1.286416882968447</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>56.64753832409679</v>
+        <v>9.205224977665729</v>
       </c>
       <c r="D5" t="n">
-        <v>24.27521427180836</v>
+        <v>3.944722319168859</v>
       </c>
       <c r="E5" t="n">
-        <v>13.69346397396203</v>
+        <v>2.22518789576883</v>
       </c>
       <c r="F5" t="n">
-        <v>7.916411587498134</v>
+        <v>1.286416882968447</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.3962462098482</v>
+        <v>3.314390009100333</v>
       </c>
       <c r="D6" t="n">
-        <v>35.99133993913822</v>
+        <v>5.848592740109961</v>
       </c>
       <c r="E6" t="n">
-        <v>13.69346397396203</v>
+        <v>2.22518789576883</v>
       </c>
       <c r="F6" t="n">
-        <v>7.916411587498134</v>
+        <v>1.286416882968447</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.16513242196523</v>
+        <v>3.11433401856935</v>
       </c>
       <c r="D7" t="n">
-        <v>39.50309092895383</v>
+        <v>6.419252275954998</v>
       </c>
       <c r="E7" t="n">
-        <v>13.69346397396203</v>
+        <v>2.22518789576883</v>
       </c>
       <c r="F7" t="n">
-        <v>7.916411587498134</v>
+        <v>1.286416882968447</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
